--- a/nr-change-system-pr/ig/StructureDefinition-as-dp-healthcareservice-social-equipment.xlsx
+++ b/nr-change-system-pr/ig/StructureDefinition-as-dp-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:31:08+00:00</t>
+    <t>2024-06-05T11:33:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
